--- a/excel/锌.xlsx
+++ b/excel/锌.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE47"/>
+  <dimension ref="A1:AG47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,8 +520,8 @@
     <col width="8" customWidth="1" min="21" max="21"/>
     <col width="8" customWidth="1" min="22" max="22"/>
     <col width="9" customWidth="1" min="23" max="23"/>
-    <col width="9" customWidth="1" min="24" max="24"/>
-    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
@@ -648,40 +648,50 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>26Q3</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>26Q3同比</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>变化原因</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>FY2026指引</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>成本（$/t）</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>FY2024资本开支(百万)</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>FY2025资本开支(百万)</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>2026Q1资本开支(百万)</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>资本开支备注</t>
         </is>
@@ -766,17 +776,20 @@
         <f>IF(AND(ISNUMBER(V2),ISNUMBER(O2),O2&lt;&gt;0),(V2-O2)/O2,"-")</f>
         <v/>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>26Q2采矿金属26.8万吨创同期新高(品位改善)；精炼锌21.3万吨(+6%)</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>109-110</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1025-1050</t>
         </is>
@@ -861,17 +874,17 @@
         <f>IF(AND(ISNUMBER(V3),ISNUMBER(O3),O3&lt;&gt;0),(V3-O3)/O3,"-")</f>
         <v/>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>26Q2: Gamsberg一期环比+10%至4.5万吨；二期2026年7月起投产</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>18-20</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1250-1350</t>
         </is>
@@ -956,12 +969,12 @@
         <f>IF(AND(ISNUMBER(V4),ISNUMBER(O4),O4&lt;&gt;0),(V4-O4)/O4,"-")</f>
         <v/>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>浮选回收率提高；26Q2: Deeps矿山接近闭坑，产量0.3万吨(-73%)</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>5.5-6.5</t>
         </is>
@@ -1046,17 +1059,17 @@
         <f>IF(AND(ISNUMBER(V5),ISNUMBER(O5),O5&lt;&gt;0),(V5-O5)/O5,"-")</f>
         <v/>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>品位和采选顺序如期上升；26Q2: 入选铜锌矿比例降至33%(去年同期77%)，矿山计划所致</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>无同口径指引（行数据为 100% 口径；Teck 权益 22.5%，权益估算 15.6-20 万吨不可直接对比）</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0.8-0.9$/lb</t>
         </is>
@@ -1141,12 +1154,12 @@
         <f>IF(AND(ISNUMBER(V6),ISNUMBER(O6),O6&lt;&gt;0),(V6-O6)/O6,"-")</f>
         <v/>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>品位下降；26Q2: 品位如矿山计划下降；Q3销量指引22-27万吨(发运季7/12启动)</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>37.5-41.5</t>
         </is>
@@ -1231,12 +1244,12 @@
         <f>IF(AND(ISNUMBER(V7),ISNUMBER(O7),O7&lt;&gt;0),(V7-O7)/O7,"-")</f>
         <v/>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>26Q2: Zinc in concentrates 30.5kt(同比-4.7%)，来自Glencore 2026-H1 Production Report(PDF)；历史Kazzinc数据口径以官方报告为准</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>无单体指引（集团 FY26 锌指引 70-74 万吨：Antamina 减量+Mount Isa 资源枯竭）</t>
         </is>
@@ -1321,7 +1334,7 @@
         <f>IF(AND(ISNUMBER(V8),ISNUMBER(O8),O8&lt;&gt;0),(V8-O8)/O8,"-")</f>
         <v/>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>26Q2: Zinc in concentrates 70.0kt(同比+4.8%)，来自Glencore 2026-H1 Production Report；历史数据与官方报告Zinc in concentrates口径吻合</t>
         </is>
@@ -1406,7 +1419,7 @@
         <f>IF(AND(ISNUMBER(V9),ISNUMBER(O9),O9&lt;&gt;0),(V9-O9)/O9,"-")</f>
         <v/>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>26Q2: Zinc in concentrates 39.1kt(同比-46.1%)，来自Glencore 2026-H1 Production Report；历史数据与官方报告Zinc in concentrates口径吻合</t>
         </is>
@@ -1491,12 +1504,12 @@
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
         <v/>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>2Q26：品位升至1.64%+block caving投产，产量同比-6.1%</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>12.8-14.5（Nexa 2026 官方指引，中枢 +6%；原 10-11 为旧值已更正）</t>
         </is>
@@ -1581,12 +1594,12 @@
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
         <v/>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>2Q26：同比+18.8%，运营改善</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>12.8-14.5（Nexa 2026 官方指引，中枢 +6%；原 10-11 为旧值已更正）</t>
         </is>
@@ -1671,12 +1684,12 @@
         <f>IF(AND(ISNUMBER(V12),ISNUMBER(O12),O12&lt;&gt;0),(V12-O12)/O12,"-")</f>
         <v/>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>Q2 将 2026 磨矿指引 1.8→1.6Mt（开拓进度不及预期），H2 偏弱</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>5.5-6.5（磨矿指引 1.6Mt 折算；Q2 由 1.8Mt 下调，开拓进度不及预期）</t>
         </is>
@@ -1761,12 +1774,12 @@
         <f>IF(AND(ISNUMBER(V13),ISNUMBER(O13),O13&lt;&gt;0),(V13-O13)/O13,"-")</f>
         <v/>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>3/14 异常地震+岩爆停产至 4 月底，Q2 磨矿仅约 0.1Mt；受损提升机已修复、未受影响区域复产，目前约 30% 产能；2027 磨矿指引 2.3Mt</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>3.2-3.5（地震后 2026 磨矿指引 1.5Mt×品位 2.7% 折算金属量；原 3.7Mt 指引已下调约 60%）</t>
         </is>
@@ -1851,12 +1864,12 @@
         <f>IF(AND(ISNUMBER(V14),ISNUMBER(O14),O14&lt;&gt;0),(V14-O14)/O14,"-")</f>
         <v/>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>一季度强降雨影响；26Q2锌2.79万吨(+7%): 磨矿量环比回升、品位稳定</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>10.5-11.5</t>
         </is>
@@ -1941,12 +1954,12 @@
         <f>IF(AND(ISNUMBER(V15),ISNUMBER(O15),O15&lt;&gt;0),(V15-O15)/O15,"-")</f>
         <v/>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>品位和回收率环比上升；26Q2锌1.68万吨(-24%): 磨矿量环比下降，锌品位升高部分对冲</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>7.5-8.5</t>
         </is>
@@ -2031,12 +2044,12 @@
         <f>IF(AND(ISNUMBER(V16),ISNUMBER(O16),O16&lt;&gt;0),(V16-O16)/O16,"-")</f>
         <v/>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>品位下降；26Q2锌4.61万吨(+6%): 磨矿量提高+锌回收率保持90%以上</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>17-18</t>
         </is>
@@ -2121,12 +2134,12 @@
         <f>IF(AND(ISNUMBER(V17),ISNUMBER(O17),O17&lt;&gt;0),(V17-O17)/O17,"-")</f>
         <v/>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>开采顺序影响；26Q2锌0.95万吨(-25%): 锌品位下降，金银副产增加使锌当量3.36万吨同比持平；C1指引下调至-1.5~-1.0$/lb</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>4.5-5.5</t>
         </is>
@@ -2208,12 +2221,12 @@
         <f>IF(AND(ISNUMBER(V18),ISNUMBER(O18),O18&lt;&gt;0),(V18-O18)/O18,"-")</f>
         <v/>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>26Q2: 副产锌品位下降(环比-35%/同比-40%)；修正25Q4=4.6万吨(官方46kt，原0.09笔误)</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -2273,12 +2286,12 @@
         <f>IF(AND(ISNUMBER(V19),ISNUMBER(O19),O19&lt;&gt;0),(V19-O19)/O19,"-")</f>
         <v/>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>私有化后无公开披露：Polymetal 2024/3/7出售全部俄罗斯资产后更名Solidcore（仅剩哈萨克资产，26Q2季报2026/9/9才发布且不含Ozernoye）；俄资产无公开季度产量（2026-08-31核：akm.ru + solidcore-resources.com）</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>预计10左右</t>
         </is>
@@ -2363,12 +2376,12 @@
         <f>IF(AND(ISNUMBER(V20),ISNUMBER(O20),O20&lt;&gt;0),(V20-O20)/O20,"-")</f>
         <v/>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>进入高品位区进展较慢；26Q2锌1.14万吨(同比+8%/环比+25%)：地下采矿率自3月洪水影响中恢复+平均品位回升；FY26锌3.92万吨(-12%)，ZnEq 20.54万吨超指引2%，销量随铁路恢复去库存</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>4（FY26实际3.92超指引2%；FY27 ZnEq指引20.47万吨不变）</t>
         </is>
@@ -2455,12 +2468,12 @@
         <f>IF(AND(ISNUMBER(V21),ISNUMBER(O21),O21&lt;&gt;0),(V21-O21)/O21,"-")</f>
         <v/>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>South32 FY26 Q4季报（2026-07-20，Investegate全文核对）锌资产仅Cannington(澳)+Hermosa Taylor(美,在建)，无任何墨西哥/Capela资产披露，26Q2无数可填</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>归属存疑（2026-08-31核）：South32资产组合中无墨西哥锌矿，「墨西哥Capela等」挂South32名下疑为历史错位；未擅自改历史行归属，26Q2标-</t>
         </is>
@@ -2530,12 +2543,12 @@
         <f>IF(AND(ISNUMBER(V22),ISNUMBER(O22),O22&lt;&gt;0),(V22-O22)/O22,"-")</f>
         <v/>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>26Q2创纪录：处理量20.1万吨/品位38.7%/回收率92%均创纪录，5月单月2.57万吨；拟合值：True</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>24-29万吨；C1 $0.85-0.95/lb；资本开支指引$60M(100%口径)</t>
         </is>
@@ -2590,12 +2603,12 @@
         <f>IF(AND(ISNUMBER(V23),ISNUMBER(O23),O23&lt;&gt;0),(V23-O23)/O23,"-")</f>
         <v/>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>中报累计相减推算：2026H1矿山产锌（锌精矿含锌）176,922吨（同比-1.5%，中报全文p11）−26Q1官方季报84,509吨=92,413吨（26Q2，同比+1.1%）；摘要「矿产锌(铅)20万吨」为锌+铅合计口径未采用。来源：cninfo紫金2026半年报（2026-08-22，1225493590.PDF）</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>矿产锌（铅）40万吨（公司规划为锌+铅合计口径）</t>
         </is>
@@ -2650,7 +2663,7 @@
         <f>IF(AND(ISNUMBER(V24),ISNUMBER(O24),O24&lt;&gt;0),(V24-O24)/O24,"-")</f>
         <v/>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>官方Informe del Director 2T26口径(含Fresnillo 74.99%+Juanicipio 100%应付，非权益)；26Q2=6.8718万吨(68,718吨)同比+14.2%(主因Tizapa复产)/环比+3.1%。来源:penoles.com.mx Informe_Director_2T26_Eng.pdf(2026-08-04)</t>
         </is>
@@ -2705,7 +2718,7 @@
         <f>IF(AND(ISNUMBER(V25),ISNUMBER(O25),O25&lt;&gt;0),(V25-O25)/O25,"-")</f>
         <v/>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>官方MD&amp;A口径（锌金属量）；25Q1/26Q1为官方累计值之差推算；Romina矿2026年6月投产爬产中（26Q2已产锌0.14万吨）</t>
         </is>
@@ -2760,12 +2773,12 @@
         <f>IF(AND(ISNUMBER(V26),ISNUMBER(O26),O26&lt;&gt;0),(V26-O26)/O26,"-")</f>
         <v/>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>官方新闻稿口径；2025年+36%主因Buenavista锌选厂高品位矿段；25Q1为全年减后三季推算；26Q2同比-14%（电话会披露，正式新闻稿官网403未取）</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>16.39万吨（2026年7月下调；1月16.55→4月16.68→7月16.39）</t>
         </is>
@@ -2820,12 +2833,12 @@
         <f>IF(AND(ISNUMBER(V27),ISNUMBER(O27),O27&lt;&gt;0),(V27-O27)/O27,"-")</f>
         <v/>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>官方Operational Review口径：33.75%权益应付锌(payable)，财年止6月，自然季由官方累计值推算（±0.1万吨取整误差）；FY26(止26/6)实际9.61万吨；Antamina减量</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>FY2026(止6月)9-11万吨(实际9.61万吨)；FY2027大降至3.5-5.5万吨（计划低品位）</t>
         </is>
@@ -2880,12 +2893,12 @@
         <f>IF(AND(ISNUMBER(V28),ISNUMBER(O28),O28&lt;&gt;0),(V28-O28)/O28,"-")</f>
         <v/>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>官方季报权益(attributable)口径；2025年-9%因Ciénega 25年8月起停产锌精矿+San Julián DOB关停；26Q2环比+5.9%</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>8.5-9.5万吨（权益锌；2027展望9.3-10.3万吨）</t>
         </is>
@@ -2940,12 +2953,12 @@
         <f>IF(AND(ISNUMBER(V29),ISNUMBER(O29),O29&lt;&gt;0),(V29-O29)/O29,"-")</f>
         <v/>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>26Q2=2.5万吨（推导值：H1 2026 Century应付锌45kt[8/27经营更新] − 26Q1 20kt[已披露] = 25kt；Q2单季未直接披露，9/1正式中报后复核）。FY2025 Century应付锌101kt(+22%超指引上限97.8kt)。源：Sibanye 8/27经营更新 + 2025年报(2/20)</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>8.63-9.83万吨(payable)</t>
         </is>
@@ -3000,7 +3013,7 @@
         <f>IF(AND(ISNUMBER(V30),ISNUMBER(O30),O30&lt;&gt;0),(V30-O30)/O30,"-")</f>
         <v/>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>26Q2 精矿含锌 11.3kt=1.13 万吨（+9% QoQ，处理量提升）；H1 21.7kt（+6%，品位改善）。源：KAZ Q2 2026 生产报告（8/11，SMM 快讯）</t>
         </is>
@@ -3055,12 +3068,12 @@
         <f>IF(AND(ISNUMBER(V31),ISNUMBER(O31),O31&lt;&gt;0),(V31-O31)/O31,"-")</f>
         <v/>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>26Q2 锌产量 15.6kt=1.56 万吨（Q1 12.6kt）；权益口径。源：Pan American Silver Q2 2026（8/12）</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>5.85-6.25万吨（权益）</t>
         </is>
@@ -3115,12 +3128,12 @@
         <f>IF(AND(ISNUMBER(V32),ISNUMBER(O32),O32&lt;&gt;0),(V32-O32)/O32,"-")</f>
         <v/>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>官方直接运营(100%)口径；25Q1/25Q3/26Q1为官方累计值之差推算；Tambomayo 2026年处理量计划降约65%</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>2.86-3.18万吨（2026年7月更新，原2.78-3.10）</t>
         </is>
@@ -3175,12 +3188,12 @@
         <f>IF(AND(ISNUMBER(V33),ISNUMBER(O33),O33&lt;&gt;0),(V33-O33)/O33,"-")</f>
         <v/>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>DPM Metals Q2 2026(7/30)：Vareš精矿含锌Q2=14.3Mlbs=0.6486万吨，直接披露；H1=24.3Mlbs，勾稽Q1=10.0Mlbs=0.4536万吨✓（与26Q1格一致）；应付锌销量Q2=8.8Mlbs滞后于产量（交付时点）；Vareš已宣布商产，年底达85万吨/年矿石处理速率。源：dpmmetals.com 7/30季报</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>DPM 2026精矿含锌59-71Mlbs≈2.68-3.22万吨</t>
         </is>
@@ -3235,12 +3248,12 @@
         <f>IF(AND(ISNUMBER(V34),ISNUMBER(O34),O34&lt;&gt;0),(V34-O34)/O34,"-")</f>
         <v/>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>官方新闻稿口径；25Q3曼尼托巴野火强制撤离停产约两个月（仅548吨）；26Q2环比+4.3%（Lalor品位回升）</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>1.85万吨</t>
         </is>
@@ -3274,7 +3287,7 @@
         <f>IF(AND(ISNUMBER(V35),ISNUMBER(O35),O35&lt;&gt;0),(V35-O35)/O35,"-")</f>
         <v/>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>锌资产（Neves-Corvo/Zinkgruvan）2025-04-16出售给Boliden交割完成，退出跟踪；两矿25Q1(4.89万吨)/25Q2交割前残段(0.93万吨)原属Lundin，平台该两矿历史数据已在Boliden行，此行留空防双计</t>
         </is>
@@ -3311,7 +3324,7 @@
         <f>IF(AND(ISNUMBER(V36),ISNUMBER(O36),O36&lt;&gt;0),(V36-O36)/O36,"-")</f>
         <v/>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>官方25Q1=4,913吨（精矿含锌，全部Yauricocha）；2025-08-01 Alpayana私有化完成、08-06 TSX退市，退出跟踪；退市后无公开季报（Yauricocha运营主体Corona仍在BVL披露财报）；券商表2025Y=2.54未核实</t>
         </is>
@@ -3345,7 +3358,7 @@
         <f>IF(AND(ISNUMBER(V37),ISNUMBER(O37),O37&lt;&gt;0),(V37-O37)/O37,"-")</f>
         <v/>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>Aljustrel矿2025Q3复产（Wheaton季报旁证）；私营公司无季度产量披露，各季数据未找到；券商跟踪表2026E=7.50万吨为预估；历史量级约年产锌10万吨（2022年）；2026年6月4亿欧元扩建落成</t>
         </is>
@@ -3379,7 +3392,7 @@
         <f>IF(AND(ISNUMBER(V38),ISNUMBER(O38),O38&lt;&gt;0),(V38-O38)/O38,"-")</f>
         <v/>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>非上市公司无季报；USGS 2023年氧化锌矿石30.3万吨（实物吨非金属量，注意口径陷阱）；券商跟踪表2026E=4.00万吨为下调后预估，待核实</t>
         </is>
@@ -3489,12 +3502,12 @@
         <f>IF(AND(ISNUMBER(V39),ISNUMBER(O39),O39&lt;&gt;0),(V39-O39)/O39,"-")</f>
         <v/>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>26Q2(FY27Q1,止6/30)锌 4.4Mlb=1,996吨=0.20万吨(同比-15%)：6月中主动停产安全整改+回采品位下降；Ying 1.6Mlb+GC 2.9Mlb</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>锌精矿含锌量；财年止3月（FY Q4=自然Q1）；季报（TSX/NYSE）；铅目录同步建行；2026-08-18新增骨架行，数据待回填；源：Silvercorp 6-K 2026-07-15（SEC）；磅×0.0004536=吨</t>
         </is>
@@ -3602,12 +3615,12 @@
         <f>IF(AND(ISNUMBER(V40),ISNUMBER(O40),O40&lt;&gt;0),(V40-O40)/O40,"-")</f>
         <v/>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>26Q2 Sasa 锌精矿含锌 4,812t=0.4812 万吨（+18% YoY：品位 2.73%/+9.6%）；H1=9,094t（+5%）；26Q1=H1−Q2=4,282t（推算注明）。FY26 指引 18-20kt。源：CAML H1 2026 运营更新（RNS 7/8）</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>锌精矿含锌量；自然年；季报（LSE）；铅目录同步建行；2026-08-18新增骨架行，数据待回填</t>
         </is>
@@ -3721,12 +3734,12 @@
         <f>IF(AND(ISNUMBER(V41),ISNUMBER(O41),O41&lt;&gt;0),(V41-O41)/O41,"-")</f>
         <v/>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>Hecla 2Q26(8/4)仅披露银/金金属量+精矿吨数（GC锌精矿17,990吨+LF锌精矿6,527吨），不再披露锌含金属量</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>锌精矿含锌量；自然年；季报（NYSE）≈季后3-4周；铅目录同步建行；2026-08-18新增骨架行，数据待回填；源：Hecla 2Q26 业绩新闻稿（8-K ex99.1）；含金属量口径缺官方值</t>
         </is>
@@ -3836,12 +3849,12 @@
         <f>IF(AND(ISNUMBER(V42),ISNUMBER(O42),O42&lt;&gt;0),(V42-O42)/O42,"-")</f>
         <v/>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>中报（7/30）：H1 矿产锌 63,906 吨=6.3906 万吨（半年口径，未拆季）。源：西部矿业 2026 半年度报告（巨潮 1225446414）</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>跨品种修正：原仅铅目录；A股年报+中报披露（季报无产量）；2026-08-18新增骨架行，数据待回填；中报H1矿产锌6.3906万吨，Q1未披露，两季平分拟合</t>
         </is>
@@ -3953,12 +3966,12 @@
         <f>IF(AND(ISNUMBER(V43),ISNUMBER(O43),O43&lt;&gt;0),(V43-O43)/O43,"-")</f>
         <v/>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>26Q2单季锌精矿产量3,212.51金属吨=0.3213万吨（经营公告直接披露口径）；26Q1未披露保持'-'（A股季报不披露产量）</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>跨品种修正：原仅铅目录；A股年报+中报披露（季报无产量）；2026-08-18新增骨架行，数据待回填</t>
         </is>
@@ -3994,12 +4007,12 @@
         <f>IF(AND(ISNUMBER(V44),ISNUMBER(P44),P44&lt;&gt;0),(V44-P44)/P44,"-")</f>
         <v/>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>2Q26：同比-3.7%，Q1扰动后恢复</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>来源：Nexa 2Q26 Production Report（SEC EDGAR 6-K ex99-1，2026-08-05）；2026-08-23 补录</t>
         </is>
@@ -4035,12 +4048,12 @@
         <f>IF(AND(ISNUMBER(V45),ISNUMBER(P45),P45&lt;&gt;0),(V45-P45)/P45,"-")</f>
         <v/>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>2Q26：同比-4.2%</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>来源：Nexa 2Q26 Production Report（SEC EDGAR 6-K ex99-1，2026-08-05）；2026-08-23 补录</t>
         </is>
@@ -4076,12 +4089,12 @@
         <f>IF(AND(ISNUMBER(V46),ISNUMBER(P46),P46&lt;&gt;0),(V46-P46)/P46,"-")</f>
         <v/>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>2Q26：同比+43.8%；Q1创纪录13kt，Q2尾矿过滤机投产过渡季</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>来源：Nexa 2Q26 Production Report（SEC EDGAR 6-K ex99-1，2026-08-05）；2026-08-23 补录</t>
         </is>
@@ -4171,7 +4184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:AB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4197,7 +4210,8 @@
     <col width="8" customWidth="1" min="21" max="21"/>
     <col width="8" customWidth="1" min="22" max="22"/>
     <col width="8" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4318,15 +4332,25 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>26Q3</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>26Q3同比</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>变化原因</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>FY2026指引</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -4406,7 +4430,7 @@
         <f>IF(AND(ISNUMBER(V2),ISNUMBER(O2),O2&lt;&gt;0),(V2-O2)/O2,"-")</f>
         <v/>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>逐步复产，年底预计满产；26Q2锌3.98万吨(-13%/环比+20%): 扩产爬坡慢于预期(新焙烧炉问题)</t>
         </is>
@@ -4486,7 +4510,7 @@
         <f>IF(AND(ISNUMBER(V3),ISNUMBER(O3),O3&lt;&gt;0),(V3-O3)/O3,"-")</f>
         <v/>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>三井金属FY27/3期Q1(2026.4-6)决算说明资料(8/7)：亜鉛生産量45千t=4.5万吨(短信仅财务口径,产量在说明资料)；通期计划218千t(8/7修正)</t>
         </is>
@@ -4568,7 +4592,7 @@
         <f>IF(AND(ISNUMBER(V4),ISNUMBER(O4),O4&lt;&gt;0),(V4-O4)/O4,"-")</f>
         <v/>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Korea Zinc Q2财报(8/6)仅披露锌销量146,374MT(standalone,-2.8%YoY)；产量年度才披露(2025年600,006MT)</t>
         </is>
@@ -4648,7 +4672,7 @@
         <f>IF(AND(ISNUMBER(V5),ISNUMBER(O5),O5&lt;&gt;0),(V5-O5)/O5,"-")</f>
         <v/>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>26Q2锌22.09万吨(-6.2%): 运营中断和电力限制；来自Glencore 2026-H1 Report(PDF, 2026-07-29)</t>
         </is>
@@ -4728,7 +4752,7 @@
         <f>IF(AND(ISNUMBER(V6),ISNUMBER(O6),O6&lt;&gt;0),(V6-O6)/O6,"-")</f>
         <v/>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>扩产投料；26Q2锌6.53万吨(-9%): 计划检修+锅炉/焙烧炉工艺扰动</t>
         </is>
@@ -4808,12 +4832,12 @@
         <f>IF(AND(ISNUMBER(V7),ISNUMBER(O7),O7&lt;&gt;0),(V7-O7)/O7,"-")</f>
         <v/>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Nexa 2Q26报告分厂表：锌金属产量33.7kt（同比+18.2%/环比-7.2%）；口径=锌金属（不含氧化锌9.1kt），与历史行一致。来源：SEC 6-K ex99-1（2026-08-05）</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>26Q2已入库：Nexa 2Q26起分厂表披露（此前8/23注「分厂未披露」已被证伪，以分厂表为准）</t>
         </is>
@@ -4893,12 +4917,12 @@
         <f>IF(AND(ISNUMBER(V8),ISNUMBER(O8),O8&lt;&gt;0),(V8-O8)/O8,"-")</f>
         <v/>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>26Q2=3.5532万吨(35,532吨)同比-33.9%(年度计划检修+复产延迟+检修前额外停车，一次性扰动非趋势减产)/H1=8.3658万吨。来源:penoles.com.mx Informe_Director_2T26_Eng.pdf(2026-08-04)</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>26Q2 Nexa冶炼锌金属+氧化合计125kt(-10%)；分冶炼厂数据未单独披露，待补充</t>
         </is>
@@ -4978,7 +5002,7 @@
         <f>IF(AND(ISNUMBER(V9),ISNUMBER(O9),O9&lt;&gt;0),(V9-O9)/O9,"-")</f>
         <v/>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>副产品利润推动纯冶炼成本下滑；26Q2: 铅回路计划检修(已含年度指引)</t>
         </is>
@@ -5058,12 +5082,12 @@
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
         <v/>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>Nexa 2Q26报告分厂表：锌金属62.0kt（同比-26.1%/环比-27.4%）；5月火灾致铸造车间停产（估计影响约7kt），6月恢复正常，受影响量预计2H26补回，全年销量指引维持。来源：SEC 6-K ex99-1（2026-08-05）</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>26Q2已入库：Nexa 2Q26分厂表（此前8/23注「分厂未披露」已被证伪）</t>
         </is>
@@ -5145,12 +5169,12 @@
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
         <v/>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>公开渠道无法获取分季度精炼锌产量。口径提示:SMC=Sun Metals Corporation(Korea Zinc 100%澳洲子公司Townsville，非韩国本土第二大冶炼厂)，非上市私人子公司不披露季度产量，集团亦不按分厂披露。来源:Korea Zinc IR/DART+Sun Metals官网+AFR｜2026-08-31核：Korea Zinc 2Q26 IR（2026-08-06）SMC章节仅披露营收/利润（销售$299.0M、OP $7.9M），未再披露分季锌产量（25Q2及之前曾披露，25Q2=65,546t），26Q2标-；报告称物流正常化后产量已恢复</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>26Q2=-：Korea Zinc 2Q26 IR未披露SMC锌产量（此前8/23误贴Nexa 125kt注，已更正）</t>
         </is>
@@ -5230,7 +5254,10 @@
         <f>IF(AND(ISNUMBER(V12),ISNUMBER(O12),O12&lt;&gt;0),(V12-O12)/O12,"-")</f>
         <v/>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X12" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>副产品受益；26Q2精炼锌21.3万吨(+6%): Chanderiya/Dariba去瓶颈+Debari 160ktpa焙烧炉释放产能，部分被计划检修抵消</t>
         </is>
@@ -5368,12 +5395,12 @@
         <f>IF(AND(ISNUMBER(V14),ISNUMBER(O14),O14&lt;&gt;0),(V14-O14)/O14,"-")</f>
         <v/>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>株冶集团2026中报仅财务口径（营收141.5亿+35.9%/净利19.5亿+232.7%），未披露锌锭产量吨数（仅相对表述"析出锌超时序进度0.64%"）</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>源：株冶集团2026年半年度报告（SSE）；产能锚点68万吨锌产品</t>
         </is>
@@ -5483,7 +5510,7 @@
         <f>IF(AND(ISNUMBER(V15),ISNUMBER(O15),O15&lt;&gt;0),(V15-O15)/O15,"-")</f>
         <v/>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>锌业股份H1 2026锌金属产品12.53万吨（安泰科口径，约占国内4%）；26Q1未披露，26Q1=26Q2=12.53/2=6.265万吨（H1/2拟合，中报无分季拆分）</t>
         </is>
@@ -6120,7 +6147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6655,6 +6682,23 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>开 26Q3 列。Vedanta Q2FY27(7-9月)入库：Zinc India 采矿金属 27.1万吨(+5% YoY)→锌矿 Vedanta 行；HZL 精炼锌 21.2万吨(+5%)→冶炼 Zawar &amp; Rampura 行。Zinc International 采矿 5.3万吨(-12%，Gamsberg 二期已投产、10 月商业放量)——锌矿表 Zinc India/Zinc International 两行历史值口径存疑，本季暂不写入，待核口径。</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Vedanta Q2FY27 Production Release 2026-10-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel/锌.xlsx
+++ b/excel/锌.xlsx
@@ -2543,14 +2543,20 @@
         <f>IF(AND(ISNUMBER(V22),ISNUMBER(O22),O22&lt;&gt;0),(V22-O22)/O22,"-")</f>
         <v/>
       </c>
+      <c r="X22" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>34.9</v>
+      </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>26Q2创纪录：处理量20.1万吨/品位38.7%/回收率92%均创纪录，5月单月2.57万吨；拟合值：True</t>
+          <t>26Q3再创纪录7.71万吨(环比+10%)：入选品位41.6%与回收率96%双纪录，7月单月2.66万吨纪录；连续7个季度环比增长，年化约30.9万吨（Ivanhoe 10/8公告）</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>24-29万吨；C1 $0.85-0.95/lb；资本开支指引$60M(100%口径)</t>
+          <t>24-29万吨；C1 $0.85-0.95/lb；资本开支指引$60M(100%口径)；10/8公告：产量将奔指引上限</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6699,6 +6705,30 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ivanhoe Kipushi 26Q3=7.71万吨入库（官方新闻稿，精矿含锌77,147吨纪录，环比+10%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ivanhoe 26Q3 更正变化原因（处理量实为19.4万吨/Q2的20.1万吨才是纪录，此前误写21.4万吨）；补26Q3同比+34.9%（表内口径）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel/锌.xlsx
+++ b/excel/锌.xlsx
@@ -3326,6 +3326,11 @@
         <f>IF(AND(ISNUMBER(T36),ISNUMBER(N36),N36&lt;&gt;0),(T36-N36)/N36,"-")</f>
         <v/>
       </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="W36">
         <f>IF(AND(ISNUMBER(V36),ISNUMBER(O36),O36&lt;&gt;0),(V36-O36)/O36,"-")</f>
         <v/>
@@ -6153,7 +6158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6729,6 +6734,23 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>26Q2 缺口复核（锌矿/冶炼）：Polymetal 维持'-'（Solidcore Q2'26 产量报告 7/31 仅哈萨克 Kyzyl/Varvara 金，俄资产 2024/3 已售、Ozernoye 无任何披露）；Sierra Metals 26Q2 空格规整为'-'（Alpayana 2025/8/1 完成私有化，无公开季报；另注：Santacruz 季报的 Bolivar 矿在玻利维亚，与 Sierra 墨西哥 Bolivar 同名不同矿，非数据源）；Korea Zinc/SMC 维持'-'（Q2'26 IR 8/6 起不披露分厂/季度锌产量，仅销量 146,374MT）；South32 Cannington 26Q2=1.14 此前已入。26Q3 早鸟：South32 FY27Q1 季报预计 10/20 前后，截至今日未发布。</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Solidcore Q2 2026 production results(2026-07-31 solidcore-resources.com)；Korea Zinc 2Q26 IR(2026-08-06)；Santacruz Silver 官网(2026-07-30)；Junior Mining Network(Alpayana 私有化)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel/锌.xlsx
+++ b/excel/锌.xlsx
@@ -779,6 +779,10 @@
       <c r="X2" t="n">
         <v>27.1</v>
       </c>
+      <c r="Y2">
+        <f>IF(AND(ISNUMBER(X2),ISNUMBER(P2),P2&lt;&gt;0),(X2-P2)/P2,"-")</f>
+        <v/>
+      </c>
       <c r="Z2" t="inlineStr">
         <is>
           <t>26Q2采矿金属26.8万吨创同期新高(品位改善)；精炼锌21.3万吨(+6%)</t>
@@ -874,9 +878,16 @@
         <f>IF(AND(ISNUMBER(V3),ISNUMBER(O3),O3&lt;&gt;0),(V3-O3)/O3,"-")</f>
         <v/>
       </c>
+      <c r="X3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y3">
+        <f>IF(AND(ISNUMBER(X3),ISNUMBER(P3),P3&lt;&gt;0),(X3-P3)/P3,"-")</f>
+        <v/>
+      </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>26Q2: Gamsberg一期环比+10%至4.5万吨；二期2026年7月起投产</t>
+          <t>26Q3 Gamsberg锌4.6万吨，环比+1%；二期已投产、10月起贡献可销售产量；Vedanta Q2FY27官方公告</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -969,9 +980,16 @@
         <f>IF(AND(ISNUMBER(V4),ISNUMBER(O4),O4&lt;&gt;0),(V4-O4)/O4,"-")</f>
         <v/>
       </c>
+      <c r="X4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Y4">
+        <f>IF(AND(ISNUMBER(X4),ISNUMBER(P4),P4&lt;&gt;0),(X4-P4)/P4,"-")</f>
+        <v/>
+      </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>浮选回收率提高；26Q2: Deeps矿山接近闭坑，产量0.3万吨(-73%)</t>
+          <t>26Q3 BMM锌0.7万吨（Zinc International总量53kt−Gamsberg 46kt推算），BMM工厂运行趋稳；Vedanta Q2FY27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1059,6 +1077,15 @@
         <f>IF(AND(ISNUMBER(V5),ISNUMBER(O5),O5&lt;&gt;0),(V5-O5)/O5,"-")</f>
         <v/>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <f>IF(AND(ISNUMBER(X5),ISNUMBER(P5),P5&lt;&gt;0),(X5-P5)/P5,"-")</f>
+        <v/>
+      </c>
       <c r="Z5" t="inlineStr">
         <is>
           <t>品位和采选顺序如期上升；26Q2: 入选铜锌矿比例降至33%(去年同期77%)，矿山计划所致</t>
@@ -1154,6 +1181,15 @@
         <f>IF(AND(ISNUMBER(V6),ISNUMBER(O6),O6&lt;&gt;0),(V6-O6)/O6,"-")</f>
         <v/>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <f>IF(AND(ISNUMBER(X6),ISNUMBER(P6),P6&lt;&gt;0),(X6-P6)/P6,"-")</f>
+        <v/>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>品位下降；26Q2: 品位如矿山计划下降；Q3销量指引22-27万吨(发运季7/12启动)</t>
@@ -1244,6 +1280,15 @@
         <f>IF(AND(ISNUMBER(V7),ISNUMBER(O7),O7&lt;&gt;0),(V7-O7)/O7,"-")</f>
         <v/>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <f>IF(AND(ISNUMBER(X7),ISNUMBER(P7),P7&lt;&gt;0),(X7-P7)/P7,"-")</f>
+        <v/>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>26Q2: Zinc in concentrates 30.5kt(同比-4.7%)，来自Glencore 2026-H1 Production Report(PDF)；历史Kazzinc数据口径以官方报告为准</t>
@@ -1334,6 +1379,15 @@
         <f>IF(AND(ISNUMBER(V8),ISNUMBER(O8),O8&lt;&gt;0),(V8-O8)/O8,"-")</f>
         <v/>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <f>IF(AND(ISNUMBER(X8),ISNUMBER(P8),P8&lt;&gt;0),(X8-P8)/P8,"-")</f>
+        <v/>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>26Q2: Zinc in concentrates 70.0kt(同比+4.8%)，来自Glencore 2026-H1 Production Report；历史数据与官方报告Zinc in concentrates口径吻合</t>
@@ -1419,6 +1473,15 @@
         <f>IF(AND(ISNUMBER(V9),ISNUMBER(O9),O9&lt;&gt;0),(V9-O9)/O9,"-")</f>
         <v/>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <f>IF(AND(ISNUMBER(X9),ISNUMBER(P9),P9&lt;&gt;0),(X9-P9)/P9,"-")</f>
+        <v/>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>26Q2: Zinc in concentrates 39.1kt(同比-46.1%)，来自Glencore 2026-H1 Production Report；历史数据与官方报告Zinc in concentrates口径吻合</t>
@@ -1504,6 +1567,15 @@
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
         <v/>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <f>IF(AND(ISNUMBER(X10),ISNUMBER(P10),P10&lt;&gt;0),(X10-P10)/P10,"-")</f>
+        <v/>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>2Q26：品位升至1.64%+block caving投产，产量同比-6.1%</t>
@@ -1594,6 +1666,15 @@
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
         <v/>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <f>IF(AND(ISNUMBER(X11),ISNUMBER(P11),P11&lt;&gt;0),(X11-P11)/P11,"-")</f>
+        <v/>
+      </c>
       <c r="Z11" t="inlineStr">
         <is>
           <t>2Q26：同比+18.8%，运营改善</t>
@@ -1684,6 +1765,15 @@
         <f>IF(AND(ISNUMBER(V12),ISNUMBER(O12),O12&lt;&gt;0),(V12-O12)/O12,"-")</f>
         <v/>
       </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <f>IF(AND(ISNUMBER(X12),ISNUMBER(P12),P12&lt;&gt;0),(X12-P12)/P12,"-")</f>
+        <v/>
+      </c>
       <c r="Z12" t="inlineStr">
         <is>
           <t>Q2 将 2026 磨矿指引 1.8→1.6Mt（开拓进度不及预期），H2 偏弱</t>
@@ -1774,6 +1864,15 @@
         <f>IF(AND(ISNUMBER(V13),ISNUMBER(O13),O13&lt;&gt;0),(V13-O13)/O13,"-")</f>
         <v/>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <f>IF(AND(ISNUMBER(X13),ISNUMBER(P13),P13&lt;&gt;0),(X13-P13)/P13,"-")</f>
+        <v/>
+      </c>
       <c r="Z13" t="inlineStr">
         <is>
           <t>3/14 异常地震+岩爆停产至 4 月底，Q2 磨矿仅约 0.1Mt；受损提升机已修复、未受影响区域复产，目前约 30% 产能；2027 磨矿指引 2.3Mt</t>
@@ -1864,6 +1963,15 @@
         <f>IF(AND(ISNUMBER(V14),ISNUMBER(O14),O14&lt;&gt;0),(V14-O14)/O14,"-")</f>
         <v/>
       </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <f>IF(AND(ISNUMBER(X14),ISNUMBER(P14),P14&lt;&gt;0),(X14-P14)/P14,"-")</f>
+        <v/>
+      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>一季度强降雨影响；26Q2锌2.79万吨(+7%): 磨矿量环比回升、品位稳定</t>
@@ -1954,6 +2062,15 @@
         <f>IF(AND(ISNUMBER(V15),ISNUMBER(O15),O15&lt;&gt;0),(V15-O15)/O15,"-")</f>
         <v/>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <f>IF(AND(ISNUMBER(X15),ISNUMBER(P15),P15&lt;&gt;0),(X15-P15)/P15,"-")</f>
+        <v/>
+      </c>
       <c r="Z15" t="inlineStr">
         <is>
           <t>品位和回收率环比上升；26Q2锌1.68万吨(-24%): 磨矿量环比下降，锌品位升高部分对冲</t>
@@ -2044,9 +2161,16 @@
         <f>IF(AND(ISNUMBER(V16),ISNUMBER(O16),O16&lt;&gt;0),(V16-O16)/O16,"-")</f>
         <v/>
       </c>
+      <c r="X16" t="n">
+        <v>4.7784</v>
+      </c>
+      <c r="Y16">
+        <f>IF(AND(ISNUMBER(X16),ISNUMBER(P16),P16&lt;&gt;0),(X16-P16)/P16,"-")</f>
+        <v/>
+      </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>品位下降；26Q2锌4.61万吨(+6%): 磨矿量提高+锌回收率保持90%以上</t>
+          <t>26Q3 Dugald River锌47,784吨=4.7784万吨，同比-1%，品位及回收率支撑；MMG Q3</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2134,14 +2258,21 @@
         <f>IF(AND(ISNUMBER(V17),ISNUMBER(O17),O17&lt;&gt;0),(V17-O17)/O17,"-")</f>
         <v/>
       </c>
+      <c r="X17" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="Y17">
+        <f>IF(AND(ISNUMBER(X17),ISNUMBER(P17),P17&lt;&gt;0),(X17-P17)/P17,"-")</f>
+        <v/>
+      </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>开采顺序影响；26Q2锌0.95万吨(-25%): 锌品位下降，金银副产增加使锌当量3.36万吨同比持平；C1指引下调至-1.5~-1.0$/lb</t>
+          <t>26Q3 Rosebery锌8,130吨=0.813万吨，同比-23%：X-South地震后可用矿量下降；全年指引下调至3.2-3.7万吨；MMG Q3</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>4.5-5.5</t>
+          <t>3.2-3.7（MMG 10/14由4.5-5.5下调）</t>
         </is>
       </c>
     </row>
@@ -2221,9 +2352,16 @@
         <f>IF(AND(ISNUMBER(V18),ISNUMBER(O18),O18&lt;&gt;0),(V18-O18)/O18,"-")</f>
         <v/>
       </c>
+      <c r="X18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Y18">
+        <f>IF(AND(ISNUMBER(X18),ISNUMBER(P18),P18&lt;&gt;0),(X18-P18)/P18,"-")</f>
+        <v/>
+      </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>26Q2: 副产锌品位下降(环比-35%/同比-40%)；修正25Q4=4.6万吨(官方46kt，原0.09笔误)</t>
+          <t>26Q3 Peñasquito锌6.7万吨，环比+68%：共产品位提高；Newmont Q3 8-K</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2286,6 +2424,15 @@
         <f>IF(AND(ISNUMBER(V19),ISNUMBER(O19),O19&lt;&gt;0),(V19-O19)/O19,"-")</f>
         <v/>
       </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <f>IF(AND(ISNUMBER(X19),ISNUMBER(P19),P19&lt;&gt;0),(X19-P19)/P19,"-")</f>
+        <v/>
+      </c>
       <c r="Z19" t="inlineStr">
         <is>
           <t>私有化后无公开披露：Polymetal 2024/3/7出售全部俄罗斯资产后更名Solidcore（仅剩哈萨克资产，26Q2季报2026/9/9才发布且不含Ozernoye）；俄资产无公开季度产量（2026-08-31核：akm.ru + solidcore-resources.com）</t>
@@ -2376,9 +2523,16 @@
         <f>IF(AND(ISNUMBER(V20),ISNUMBER(O20),O20&lt;&gt;0),(V20-O20)/O20,"-")</f>
         <v/>
       </c>
+      <c r="X20" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Y20">
+        <f>IF(AND(ISNUMBER(X20),ISNUMBER(P20),P20&lt;&gt;0),(X20-P20)/P20,"-")</f>
+        <v/>
+      </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>进入高品位区进展较慢；26Q2锌1.14万吨(同比+8%/环比+25%)：地下采矿率自3月洪水影响中恢复+平均品位回升；FY26锌3.92万吨(-12%)，ZnEq 20.54万吨超指引2%，销量随铁路恢复去库存</t>
+          <t>26Q3 Cannington应付锌8.8kt=0.88万吨，同比+6%/环比-23%；South32 FY27Q1</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2468,6 +2622,15 @@
         <f>IF(AND(ISNUMBER(V21),ISNUMBER(O21),O21&lt;&gt;0),(V21-O21)/O21,"-")</f>
         <v/>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <f>IF(AND(ISNUMBER(X21),ISNUMBER(P21),P21&lt;&gt;0),(X21-P21)/P21,"-")</f>
+        <v/>
+      </c>
       <c r="Z21" t="inlineStr">
         <is>
           <t>South32 FY26 Q4季报（2026-07-20，Investegate全文核对）锌资产仅Cannington(澳)+Hermosa Taylor(美,在建)，无任何墨西哥/Capela资产披露，26Q2无数可填</t>
@@ -2609,9 +2772,16 @@
         <f>IF(AND(ISNUMBER(V23),ISNUMBER(O23),O23&lt;&gt;0),(V23-O23)/O23,"-")</f>
         <v/>
       </c>
+      <c r="X23" t="n">
+        <v>8.073600000000001</v>
+      </c>
+      <c r="Y23">
+        <f>IF(AND(ISNUMBER(X23),ISNUMBER(P23),P23&lt;&gt;0),(X23-P23)/P23,"-")</f>
+        <v/>
+      </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>中报累计相减推算：2026H1矿山产锌（锌精矿含锌）176,922吨（同比-1.5%，中报全文p11）−26Q1官方季报84,509吨=92,413吨（26Q2，同比+1.1%）；摘要「矿产锌(铅)20万吨」为锌+铅合计口径未采用。来源：cninfo紫金2026半年报（2026-08-22，1225493590.PDF）</t>
+          <t>26Q3矿山产锌80,736吨=8.0736万吨；公司三季报直接披露单季值</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2669,6 +2839,15 @@
         <f>IF(AND(ISNUMBER(V24),ISNUMBER(O24),O24&lt;&gt;0),(V24-O24)/O24,"-")</f>
         <v/>
       </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-10-26)</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <f>IF(AND(ISNUMBER(X24),ISNUMBER(P24),P24&lt;&gt;0),(X24-P24)/P24,"-")</f>
+        <v/>
+      </c>
       <c r="Z24" t="inlineStr">
         <is>
           <t>官方Informe del Director 2T26口径(含Fresnillo 74.99%+Juanicipio 100%应付，非权益)；26Q2=6.8718万吨(68,718吨)同比+14.2%(主因Tizapa复产)/环比+3.1%。来源:penoles.com.mx Informe_Director_2T26_Eng.pdf(2026-08-04)</t>
@@ -2724,6 +2903,15 @@
         <f>IF(AND(ISNUMBER(V25),ISNUMBER(O25),O25&lt;&gt;0),(V25-O25)/O25,"-")</f>
         <v/>
       </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-10月末)</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <f>IF(AND(ISNUMBER(X25),ISNUMBER(P25),P25&lt;&gt;0),(X25-P25)/P25,"-")</f>
+        <v/>
+      </c>
       <c r="Z25" t="inlineStr">
         <is>
           <t>官方MD&amp;A口径（锌金属量）；25Q1/26Q1为官方累计值之差推算；Romina矿2026年6月投产爬产中（26Q2已产锌0.14万吨）</t>
@@ -2779,9 +2967,16 @@
         <f>IF(AND(ISNUMBER(V26),ISNUMBER(O26),O26&lt;&gt;0),(V26-O26)/O26,"-")</f>
         <v/>
       </c>
+      <c r="X26" t="n">
+        <v>4.188</v>
+      </c>
+      <c r="Y26">
+        <f>IF(AND(ISNUMBER(X26),ISNUMBER(P26),P26&lt;&gt;0),(X26-P26)/P26,"-")</f>
+        <v/>
+      </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>官方新闻稿口径；2025年+36%主因Buenavista锌选厂高品位矿段；25Q1为全年减后三季推算；26Q2同比-14%（电话会披露，正式新闻稿官网403未取）</t>
+          <t>26Q3矿产锌41,880吨=4.188万吨，同比-7.9%：Buenavista及IMMSA品位下降；SCCO 3Q26官方新闻稿</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -2839,9 +3034,16 @@
         <f>IF(AND(ISNUMBER(V27),ISNUMBER(O27),O27&lt;&gt;0),(V27-O27)/O27,"-")</f>
         <v/>
       </c>
+      <c r="X27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y27">
+        <f>IF(AND(ISNUMBER(X27),ISNUMBER(P27),P27&lt;&gt;0),(X27-P27)/P27,"-")</f>
+        <v/>
+      </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>官方Operational Review口径：33.75%权益应付锌(payable)，财年止6月，自然季由官方累计值推算（±0.1万吨取整误差）；FY26(止26/6)实际9.61万吨；Antamina减量</t>
+          <t>26Q3 Antamina应付锌11kt=1.1万吨（33.75%权益），同比-70%：计划低品位；BHP FY27Q1</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -2899,9 +3101,16 @@
         <f>IF(AND(ISNUMBER(V28),ISNUMBER(O28),O28&lt;&gt;0),(V28-O28)/O28,"-")</f>
         <v/>
       </c>
+      <c r="X28" t="n">
+        <v>2.4906</v>
+      </c>
+      <c r="Y28">
+        <f>IF(AND(ISNUMBER(X28),ISNUMBER(P28),P28&lt;&gt;0),(X28-P28)/P28,"-")</f>
+        <v/>
+      </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>官方季报权益(attributable)口径；2025年-9%因Ciénega 25年8月起停产锌精矿+San Julián DOB关停；26Q2环比+5.9%</t>
+          <t>26Q3权益锌24,906吨=2.4906万吨，同比+0.7%/环比-10%；Fresnillo 3Q26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -2959,6 +3168,15 @@
         <f>IF(AND(ISNUMBER(V29),ISNUMBER(O29),O29&lt;&gt;0),(V29-O29)/O29,"-")</f>
         <v/>
       </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-10月末Q3经营更新)</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <f>IF(AND(ISNUMBER(X29),ISNUMBER(P29),P29&lt;&gt;0),(X29-P29)/P29,"-")</f>
+        <v/>
+      </c>
       <c r="Z29" t="inlineStr">
         <is>
           <t>26Q2=2.5万吨（推导值：H1 2026 Century应付锌45kt[8/27经营更新] − 26Q1 20kt[已披露] = 25kt；Q2单季未直接披露，9/1正式中报后复核）。FY2025 Century应付锌101kt(+22%超指引上限97.8kt)。源：Sibanye 8/27经营更新 + 2025年报(2/20)</t>
@@ -3019,6 +3237,15 @@
         <f>IF(AND(ISNUMBER(V30),ISNUMBER(O30),O30&lt;&gt;0),(V30-O30)/O30,"-")</f>
         <v/>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-10月末)</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <f>IF(AND(ISNUMBER(X30),ISNUMBER(P30),P30&lt;&gt;0),(X30-P30)/P30,"-")</f>
+        <v/>
+      </c>
       <c r="Z30" t="inlineStr">
         <is>
           <t>26Q2 精矿含锌 11.3kt=1.13 万吨（+9% QoQ，处理量提升）；H1 21.7kt（+6%，品位改善）。源：KAZ Q2 2026 生产报告（8/11，SMM 快讯）</t>
@@ -3074,6 +3301,15 @@
         <f>IF(AND(ISNUMBER(V31),ISNUMBER(O31),O31&lt;&gt;0),(V31-O31)/O31,"-")</f>
         <v/>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>待发布(2026-11-04)</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <f>IF(AND(ISNUMBER(X31),ISNUMBER(P31),P31&lt;&gt;0),(X31-P31)/P31,"-")</f>
+        <v/>
+      </c>
       <c r="Z31" t="inlineStr">
         <is>
           <t>26Q2 锌产量 15.6kt=1.56 万吨（Q1 12.6kt）；权益口径。源：Pan American Silver Q2 2026（8/12）</t>
@@ -3134,9 +3370,16 @@
         <f>IF(AND(ISNUMBER(V32),ISNUMBER(O32),O32&lt;&gt;0),(V32-O32)/O32,"-")</f>
         <v/>
       </c>
+      <c r="X32" t="n">
+        <v>0.6938</v>
+      </c>
+      <c r="Y32">
+        <f>IF(AND(ISNUMBER(X32),ISNUMBER(P32),P32&lt;&gt;0),(X32-P32)/P32,"-")</f>
+        <v/>
+      </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>官方直接运营(100%)口径；25Q1/25Q3/26Q1为官方累计值之差推算；Tambomayo 2026年处理量计划降约65%</t>
+          <t>26Q3直接运营锌6,938吨=0.6938万吨（Uchucchacua 6,433+Tambomayo 505）；Buenaventura 6-K</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3194,9 +3437,16 @@
         <f>IF(AND(ISNUMBER(V33),ISNUMBER(O33),O33&lt;&gt;0),(V33-O33)/O33,"-")</f>
         <v/>
       </c>
+      <c r="X33" t="n">
+        <v>1.27008</v>
+      </c>
+      <c r="Y33">
+        <f>IF(AND(ISNUMBER(X33),ISNUMBER(P33),P33&lt;&gt;0),(X33-P33)/P33,"-")</f>
+        <v/>
+      </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>DPM Metals Q2 2026(7/30)：Vareš精矿含锌Q2=14.3Mlbs=0.6486万吨，直接披露；H1=24.3Mlbs，勾稽Q1=10.0Mlbs=0.4536万吨✓（与26Q1格一致）；应付锌销量Q2=8.8Mlbs滞后于产量（交付时点）；Vareš已宣布商产，年底达85万吨/年矿石处理速率。源：dpmmetals.com 7/30季报</t>
+          <t>26Q3 Vareš精矿含锌28Mlb=12,700.8吨=1.2701万吨，爬产强於预期；DPM 10/8初步产量公告</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3254,6 +3504,15 @@
         <f>IF(AND(ISNUMBER(V34),ISNUMBER(O34),O34&lt;&gt;0),(V34-O34)/O34,"-")</f>
         <v/>
       </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>待发布(2026-11-12)</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <f>IF(AND(ISNUMBER(X34),ISNUMBER(P34),P34&lt;&gt;0),(X34-P34)/P34,"-")</f>
+        <v/>
+      </c>
       <c r="Z34" t="inlineStr">
         <is>
           <t>官方新闻稿口径；25Q3曼尼托巴野火强制撤离停产约两个月（仅548吨）；26Q2环比+4.3%（Lalor品位回升）</t>
@@ -3293,6 +3552,10 @@
         <f>IF(AND(ISNUMBER(V35),ISNUMBER(O35),O35&lt;&gt;0),(V35-O35)/O35,"-")</f>
         <v/>
       </c>
+      <c r="Y35">
+        <f>IF(AND(ISNUMBER(X35),ISNUMBER(P35),P35&lt;&gt;0),(X35-P35)/P35,"-")</f>
+        <v/>
+      </c>
       <c r="Z35" t="inlineStr">
         <is>
           <t>锌资产（Neves-Corvo/Zinkgruvan）2025-04-16出售给Boliden交割完成，退出跟踪；两矿25Q1(4.89万吨)/25Q2交割前残段(0.93万吨)原属Lundin，平台该两矿历史数据已在Boliden行，此行留空防双计</t>
@@ -3335,6 +3598,10 @@
         <f>IF(AND(ISNUMBER(V36),ISNUMBER(O36),O36&lt;&gt;0),(V36-O36)/O36,"-")</f>
         <v/>
       </c>
+      <c r="Y36">
+        <f>IF(AND(ISNUMBER(X36),ISNUMBER(P36),P36&lt;&gt;0),(X36-P36)/P36,"-")</f>
+        <v/>
+      </c>
       <c r="Z36" t="inlineStr">
         <is>
           <t>官方25Q1=4,913吨（精矿含锌，全部Yauricocha）；2025-08-01 Alpayana私有化完成、08-06 TSX退市，退出跟踪；退市后无公开季报（Yauricocha运营主体Corona仍在BVL披露财报）；券商表2025Y=2.54未核实</t>
@@ -3369,6 +3636,10 @@
         <f>IF(AND(ISNUMBER(V37),ISNUMBER(O37),O37&lt;&gt;0),(V37-O37)/O37,"-")</f>
         <v/>
       </c>
+      <c r="Y37">
+        <f>IF(AND(ISNUMBER(X37),ISNUMBER(P37),P37&lt;&gt;0),(X37-P37)/P37,"-")</f>
+        <v/>
+      </c>
       <c r="Z37" t="inlineStr">
         <is>
           <t>Aljustrel矿2025Q3复产（Wheaton季报旁证）；私营公司无季度产量披露，各季数据未找到；券商跟踪表2026E=7.50万吨为预估；历史量级约年产锌10万吨（2022年）；2026年6月4亿欧元扩建落成</t>
@@ -3403,6 +3674,10 @@
         <f>IF(AND(ISNUMBER(V38),ISNUMBER(O38),O38&lt;&gt;0),(V38-O38)/O38,"-")</f>
         <v/>
       </c>
+      <c r="Y38">
+        <f>IF(AND(ISNUMBER(X38),ISNUMBER(P38),P38&lt;&gt;0),(X38-P38)/P38,"-")</f>
+        <v/>
+      </c>
       <c r="Z38" t="inlineStr">
         <is>
           <t>非上市公司无季报；USGS 2023年氧化锌矿石30.3万吨（实物吨非金属量，注意口径陷阱）；券商跟踪表2026E=4.00万吨为下调后预估，待核实</t>
@@ -3513,9 +3788,16 @@
         <f>IF(AND(ISNUMBER(V39),ISNUMBER(O39),O39&lt;&gt;0),(V39-O39)/O39,"-")</f>
         <v/>
       </c>
+      <c r="X39" t="n">
+        <v>0.036288</v>
+      </c>
+      <c r="Y39">
+        <f>IF(AND(ISNUMBER(X39),ISNUMBER(P39),P39&lt;&gt;0),(X39-P39)/P39,"-")</f>
+        <v/>
+      </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>26Q2(FY27Q1,止6/30)锌 4.4Mlb=1,996吨=0.20万吨(同比-15%)：6月中主动停产安全整改+回采品位下降；Ying 1.6Mlb+GC 2.9Mlb</t>
+          <t>26Q3(FY27Q2)锌0.8Mlb（Ying 0.7+GC 0.1）=362.9吨=0.0363万吨，安全整改及GC停产影响；Silvercorp 10/19</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -3626,9 +3908,16 @@
         <f>IF(AND(ISNUMBER(V40),ISNUMBER(O40),O40&lt;&gt;0),(V40-O40)/O40,"-")</f>
         <v/>
       </c>
+      <c r="X40" t="n">
+        <v>0.4968</v>
+      </c>
+      <c r="Y40">
+        <f>IF(AND(ISNUMBER(X40),ISNUMBER(P40),P40&lt;&gt;0),(X40-P40)/P40,"-")</f>
+        <v/>
+      </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>26Q2 Sasa 锌精矿含锌 4,812t=0.4812 万吨（+18% YoY：品位 2.73%/+9.6%）；H1=9,094t（+5%）；26Q1=H1−Q2=4,282t（推算注明）。FY26 指引 18-20kt。源：CAML H1 2026 运营更新（RNS 7/8）</t>
+          <t>26Q3 Sasa锌精矿含锌4,968吨=0.4968万吨，同比+18%：品位及采选量提升；CAML Q3 RNS</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -3745,6 +4034,15 @@
         <f>IF(AND(ISNUMBER(V41),ISNUMBER(O41),O41&lt;&gt;0),(V41-O41)/O41,"-")</f>
         <v/>
       </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-11上旬)</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <f>IF(AND(ISNUMBER(X41),ISNUMBER(P41),P41&lt;&gt;0),(X41-P41)/P41,"-")</f>
+        <v/>
+      </c>
       <c r="Z41" t="inlineStr">
         <is>
           <t>Hecla 2Q26(8/4)仅披露银/金金属量+精矿吨数（GC锌精矿17,990吨+LF锌精矿6,527吨），不再披露锌含金属量</t>
@@ -3860,6 +4158,15 @@
         <f>IF(AND(ISNUMBER(V42),ISNUMBER(O42),O42&lt;&gt;0),(V42-O42)/O42,"-")</f>
         <v/>
       </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-10月末)</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <f>IF(AND(ISNUMBER(X42),ISNUMBER(P42),P42&lt;&gt;0),(X42-P42)/P42,"-")</f>
+        <v/>
+      </c>
       <c r="Z42" t="inlineStr">
         <is>
           <t>中报（7/30）：H1 矿产锌 63,906 吨=6.3906 万吨（半年口径，未拆季）。源：西部矿业 2026 半年度报告（巨潮 1225446414）</t>
@@ -3977,6 +4284,15 @@
         <f>IF(AND(ISNUMBER(V43),ISNUMBER(O43),O43&lt;&gt;0),(V43-O43)/O43,"-")</f>
         <v/>
       </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-31)</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <f>IF(AND(ISNUMBER(X43),ISNUMBER(P43),P43&lt;&gt;0),(X43-P43)/P43,"-")</f>
+        <v/>
+      </c>
       <c r="Z43" t="inlineStr">
         <is>
           <t>26Q2单季锌精矿产量3,212.51金属吨=0.3213万吨（经营公告直接披露口径）；26Q1未披露保持'-'（A股季报不披露产量）</t>
@@ -4018,6 +4334,15 @@
         <f>IF(AND(ISNUMBER(V44),ISNUMBER(P44),P44&lt;&gt;0),(V44-P44)/P44,"-")</f>
         <v/>
       </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <f>IF(AND(ISNUMBER(X44),ISNUMBER(P44),P44&lt;&gt;0),(X44-P44)/P44,"-")</f>
+        <v/>
+      </c>
       <c r="Z44" t="inlineStr">
         <is>
           <t>2Q26：同比-3.7%，Q1扰动后恢复</t>
@@ -4059,6 +4384,15 @@
         <f>IF(AND(ISNUMBER(V45),ISNUMBER(P45),P45&lt;&gt;0),(V45-P45)/P45,"-")</f>
         <v/>
       </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <f>IF(AND(ISNUMBER(X45),ISNUMBER(P45),P45&lt;&gt;0),(X45-P45)/P45,"-")</f>
+        <v/>
+      </c>
       <c r="Z45" t="inlineStr">
         <is>
           <t>2Q26：同比-4.2%</t>
@@ -4100,6 +4434,15 @@
         <f>IF(AND(ISNUMBER(V46),ISNUMBER(P46),P46&lt;&gt;0),(V46-P46)/P46,"-")</f>
         <v/>
       </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <f>IF(AND(ISNUMBER(X46),ISNUMBER(P46),P46&lt;&gt;0),(X46-P46)/P46,"-")</f>
+        <v/>
+      </c>
       <c r="Z46" t="inlineStr">
         <is>
           <t>2Q26：同比+43.8%；Q1创纪录13kt，Q2尾矿过滤机投产过渡季</t>
@@ -4182,6 +4525,13 @@
       </c>
       <c r="V47" t="n">
         <v>116.126</v>
+      </c>
+      <c r="X47" t="n">
+        <v>71.630568</v>
+      </c>
+      <c r="Y47">
+        <f>IF(AND(ISNUMBER(X47),ISNUMBER(P47),P47&lt;&gt;0),(X47-P47)/P47,"-")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -4441,6 +4791,15 @@
         <f>IF(AND(ISNUMBER(V2),ISNUMBER(O2),O2&lt;&gt;0),(V2-O2)/O2,"-")</f>
         <v/>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <f>IF(AND(ISNUMBER(X2),ISNUMBER(P2),P2&lt;&gt;0),(X2-P2)/P2,"-")</f>
+        <v/>
+      </c>
       <c r="Z2" t="inlineStr">
         <is>
           <t>逐步复产，年底预计满产；26Q2锌3.98万吨(-13%/环比+20%): 扩产爬坡慢于预期(新焙烧炉问题)</t>
@@ -4521,6 +4880,15 @@
         <f>IF(AND(ISNUMBER(V3),ISNUMBER(O3),O3&lt;&gt;0),(V3-O3)/O3,"-")</f>
         <v/>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-11上旬)</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <f>IF(AND(ISNUMBER(X3),ISNUMBER(P3),P3&lt;&gt;0),(X3-P3)/P3,"-")</f>
+        <v/>
+      </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>三井金属FY27/3期Q1(2026.4-6)决算说明资料(8/7)：亜鉛生産量45千t=4.5万吨(短信仅财务口径,产量在说明资料)；通期计划218千t(8/7修正)</t>
@@ -4603,6 +4971,15 @@
         <f>IF(AND(ISNUMBER(V4),ISNUMBER(O4),O4&lt;&gt;0),(V4-O4)/O4,"-")</f>
         <v/>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <f>IF(AND(ISNUMBER(X4),ISNUMBER(P4),P4&lt;&gt;0),(X4-P4)/P4,"-")</f>
+        <v/>
+      </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>Korea Zinc Q2财报(8/6)仅披露锌销量146,374MT(standalone,-2.8%YoY)；产量年度才披露(2025年600,006MT)</t>
@@ -4683,6 +5060,15 @@
         <f>IF(AND(ISNUMBER(V5),ISNUMBER(O5),O5&lt;&gt;0),(V5-O5)/O5,"-")</f>
         <v/>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <f>IF(AND(ISNUMBER(X5),ISNUMBER(P5),P5&lt;&gt;0),(X5-P5)/P5,"-")</f>
+        <v/>
+      </c>
       <c r="Z5" t="inlineStr">
         <is>
           <t>26Q2锌22.09万吨(-6.2%): 运营中断和电力限制；来自Glencore 2026-H1 Report(PDF, 2026-07-29)</t>
@@ -4763,6 +5149,15 @@
         <f>IF(AND(ISNUMBER(V6),ISNUMBER(O6),O6&lt;&gt;0),(V6-O6)/O6,"-")</f>
         <v/>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <f>IF(AND(ISNUMBER(X6),ISNUMBER(P6),P6&lt;&gt;0),(X6-P6)/P6,"-")</f>
+        <v/>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>扩产投料；26Q2锌6.53万吨(-9%): 计划检修+锅炉/焙烧炉工艺扰动</t>
@@ -4843,6 +5238,15 @@
         <f>IF(AND(ISNUMBER(V7),ISNUMBER(O7),O7&lt;&gt;0),(V7-O7)/O7,"-")</f>
         <v/>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <f>IF(AND(ISNUMBER(X7),ISNUMBER(P7),P7&lt;&gt;0),(X7-P7)/P7,"-")</f>
+        <v/>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>Nexa 2Q26报告分厂表：锌金属产量33.7kt（同比+18.2%/环比-7.2%）；口径=锌金属（不含氧化锌9.1kt），与历史行一致。来源：SEC 6-K ex99-1（2026-08-05）</t>
@@ -4928,6 +5332,15 @@
         <f>IF(AND(ISNUMBER(V8),ISNUMBER(O8),O8&lt;&gt;0),(V8-O8)/O8,"-")</f>
         <v/>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>待发布(预计2026-10-26)</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <f>IF(AND(ISNUMBER(X8),ISNUMBER(P8),P8&lt;&gt;0),(X8-P8)/P8,"-")</f>
+        <v/>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>26Q2=3.5532万吨(35,532吨)同比-33.9%(年度计划检修+复产延迟+检修前额外停车，一次性扰动非趋势减产)/H1=8.3658万吨。来源:penoles.com.mx Informe_Director_2T26_Eng.pdf(2026-08-04)</t>
@@ -5013,6 +5426,15 @@
         <f>IF(AND(ISNUMBER(V9),ISNUMBER(O9),O9&lt;&gt;0),(V9-O9)/O9,"-")</f>
         <v/>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <f>IF(AND(ISNUMBER(X9),ISNUMBER(P9),P9&lt;&gt;0),(X9-P9)/P9,"-")</f>
+        <v/>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>副产品利润推动纯冶炼成本下滑；26Q2: 铅回路计划检修(已含年度指引)</t>
@@ -5093,6 +5515,15 @@
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
         <v/>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>待发布(2026-10-29)</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <f>IF(AND(ISNUMBER(X10),ISNUMBER(P10),P10&lt;&gt;0),(X10-P10)/P10,"-")</f>
+        <v/>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>Nexa 2Q26报告分厂表：锌金属62.0kt（同比-26.1%/环比-27.4%）；5月火灾致铸造车间停产（估计影响约7kt），6月恢复正常，受影响量预计2H26补回，全年销量指引维持。来源：SEC 6-K ex99-1（2026-08-05）</t>
@@ -5180,6 +5611,15 @@
         <f>IF(AND(ISNUMBER(V11),ISNUMBER(O11),O11&lt;&gt;0),(V11-O11)/O11,"-")</f>
         <v/>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <f>IF(AND(ISNUMBER(X11),ISNUMBER(P11),P11&lt;&gt;0),(X11-P11)/P11,"-")</f>
+        <v/>
+      </c>
       <c r="Z11" t="inlineStr">
         <is>
           <t>公开渠道无法获取分季度精炼锌产量。口径提示:SMC=Sun Metals Corporation(Korea Zinc 100%澳洲子公司Townsville，非韩国本土第二大冶炼厂)，非上市私人子公司不披露季度产量，集团亦不按分厂披露。来源:Korea Zinc IR/DART+Sun Metals官网+AFR｜2026-08-31核：Korea Zinc 2Q26 IR（2026-08-06）SMC章节仅披露营收/利润（销售$299.0M、OP $7.9M），未再披露分季锌产量（25Q2及之前曾披露，25Q2=65,546t），26Q2标-；报告称物流正常化后产量已恢复</t>
@@ -5268,6 +5708,10 @@
       <c r="X12" t="n">
         <v>21.2</v>
       </c>
+      <c r="Y12">
+        <f>IF(AND(ISNUMBER(X12),ISNUMBER(P12),P12&lt;&gt;0),(X12-P12)/P12,"-")</f>
+        <v/>
+      </c>
       <c r="Z12" t="inlineStr">
         <is>
           <t>副产品受益；26Q2精炼锌21.3万吨(+6%): Chanderiya/Dariba去瓶颈+Debari 160ktpa焙烧炉释放产能，部分被计划检修抵消</t>
@@ -5297,6 +5741,10 @@
         <f>IF(AND(ISNUMBER(V13),ISNUMBER(O13),O13&lt;&gt;0),(V13-O13)/O13,"-")</f>
         <v/>
       </c>
+      <c r="Y13">
+        <f>IF(AND(ISNUMBER(X13),ISNUMBER(P13),P13&lt;&gt;0),(X13-P13)/P13,"-")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5406,6 +5854,10 @@
         <f>IF(AND(ISNUMBER(V14),ISNUMBER(O14),O14&lt;&gt;0),(V14-O14)/O14,"-")</f>
         <v/>
       </c>
+      <c r="Y14">
+        <f>IF(AND(ISNUMBER(X14),ISNUMBER(P14),P14&lt;&gt;0),(X14-P14)/P14,"-")</f>
+        <v/>
+      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>株冶集团2026中报仅财务口径（营收141.5亿+35.9%/净利19.5亿+232.7%），未披露锌锭产量吨数（仅相对表述"析出锌超时序进度0.64%"）</t>
@@ -5519,6 +5971,10 @@
       </c>
       <c r="W15">
         <f>IF(AND(ISNUMBER(V15),ISNUMBER(O15),O15&lt;&gt;0),(V15-O15)/O15,"-")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>IF(AND(ISNUMBER(X15),ISNUMBER(P15),P15&lt;&gt;0),(X15-P15)/P15,"-")</f>
         <v/>
       </c>
       <c r="Z15" t="inlineStr">
@@ -6158,7 +6614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6751,6 +7207,40 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>锌26Q3第一批：Vedanta International(Gamsberg 4.6/BMM 0.7)、MMG(4.7784/0.813)、Newmont 6.7、South32 0.88、紫金8.0736、SCCO 4.188、BHP 1.1、Fresnillo 2.4906、Buenaventura 0.6938、DPM 1.2701、CAML 0.4968、Silvercorp 0.0363万吨入库；其余按官方披露日历标待发布/无季度披露</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Vedanta Q2FY27；MMG/Newmont/South32/BHP/Fresnillo/SCCO/Buenaventura/DPM/CAML/Silvercorp官方Q3公告；Teck/Glencore/Boliden/Nexa披露日历</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MMG Rosebery 2026锌产量指引由4.5-5.5下调至3.2-3.7万吨（X-South地震影响）</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MMG Q3 Production Report 2026-10-14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
